--- a/benchmarks/dementia_special_issue/figures/FIG2/figure2_dementia_full_cross_cohort_evidence_source_data.xlsx
+++ b/benchmarks/dementia_special_issue/figures/FIG2/figure2_dementia_full_cross_cohort_evidence_source_data.xlsx
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22T13:42:27.053631+00:00</t>
+          <t>2026-05-22T15:02:33.215989+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
